--- a/Data/Config.xlsx
+++ b/Data/Config.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Gunes Tamer Ozturk\Documents\UiPath\JobFinder\Data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5633F607-CEF2-4514-99EA-72440C122AFB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4C9D9245-14C8-42D1-8994-22DEDB155DEC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="14250" yWindow="570" windowWidth="13830" windowHeight="9615" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="61" uniqueCount="51">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="62" uniqueCount="51">
   <si>
     <t>Name</t>
   </si>
@@ -611,7 +611,9 @@
       <c r="A3" s="2" t="s">
         <v>31</v>
       </c>
-      <c r="B3" s="2"/>
+      <c r="B3" s="2" t="s">
+        <v>49</v>
+      </c>
       <c r="C3" s="4" t="s">
         <v>32</v>
       </c>
